--- a/业务合作费.xlsx
+++ b/业务合作费.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31820" windowHeight="21400"/>
+    <workbookView windowWidth="28800" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="业务合作费" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>费用名称</t>
   </si>
@@ -412,15 +412,6 @@
   </si>
   <si>
     <t>200元/台</t>
-  </si>
-  <si>
-    <t>订单清分后统计</t>
-  </si>
-  <si>
-    <t>所属小区：四川-成都、重庆-其他、四川-重启</t>
-  </si>
-  <si>
-    <t>唯普毛利*65%</t>
   </si>
   <si>
     <t>订单清分后统计
@@ -472,6 +463,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>订单清分后统计成交车辆：
 1、集团=长久集团
 2、成交台数(不抛仲裁退车)：按照</t>
@@ -546,6 +544,21 @@
   </si>
   <si>
     <r>
+      <t>订单清分后统计成交车辆：
+1、集团=昊诚集团
+2、成交台数(不抛仲裁退车)：按照合同年计算；比如26年的成交台数中的合同年指统计：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025.9.1-</t>
+    </r>
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -553,9 +566,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">订单清分后统计成交车辆：
-1、集团=昊诚集团
-2、成交台数(不抛仲裁退车)：按照合同年计算；比如26年的成交台数中的合同年指统计：2025.7.31-至今的成交总台数
+      <t xml:space="preserve">至今的成交总台数
 3、报废车和非报废车标准不同
 4、限定门店自拍账号不纳入
 </t>
@@ -611,10 +622,23 @@
     </r>
   </si>
   <si>
-    <t>次月1日0点统计成交车辆：
+    <r>
+      <t xml:space="preserve">次月1日0点统计成交车辆：
 1、门店id=4447，门店全称：桂林长久鑫广达二手车销售有限公司
 2、门店每月总费用2500元/月；
-3、每台车平均业务合作费(2500/成交台次)汇总=2500元/月</t>
+3、每台车平均业务合作费(2500/成交台次)汇总=2500元/月
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>如果本月无成交，固定业务合作费(场地费)2500元，挂在虚拟车牌上，车牌虚A00001，业务员：黄缵；</t>
+    </r>
   </si>
   <si>
     <t>桂林长久鑫广达二手车销售有限公司</t>
@@ -623,10 +647,23 @@
     <t>固定：2500元/月</t>
   </si>
   <si>
-    <t>次月1日0点统计成交车辆：
+    <r>
+      <t xml:space="preserve">次月1日0点统计成交车辆：
 1、门店id=4448，门店全称：广西长久二手车销售有限公司
 2、门店每月总费用4500元/月；
-3、每台车平均业务合作费(2500/成交台次)汇总=2500元/月</t>
+3、每台车平均业务合作费(2500/成交台次)汇总=2500元/月
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>如果本月无成交，固定业务合作费(场地费)4500元，挂在虚拟车牌上，车牌虚B00001，业务员：黄缵；</t>
+    </r>
   </si>
   <si>
     <t>广西长久二手车销售有限公司</t>
@@ -675,7 +712,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,6 +895,13 @@
     <font>
       <sz val="11"/>
       <color theme="4" tint="0.4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1432,7 +1476,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1467,9 +1511,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2045,11 +2086,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="25.9519230769231" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.6923076923077" customWidth="1"/>
-    <col min="2" max="2" width="51.0096153846154" customWidth="1"/>
+    <col min="2" max="2" width="57.9615384615385" customWidth="1"/>
     <col min="3" max="3" width="36.9903846153846" customWidth="1"/>
     <col min="4" max="4" width="38.7788461538462" customWidth="1"/>
     <col min="5" max="5" width="29.3269230769231" customWidth="1"/>
@@ -2088,10 +2129,10 @@
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2106,10 +2147,10 @@
       <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2124,10 +2165,10 @@
       <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="20" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2142,202 +2183,184 @@
       <c r="D5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="34" spans="1:6">
+    <row r="6" ht="51" spans="1:6">
       <c r="A6" s="2"/>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>10</v>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7" ht="51" spans="1:6">
+    <row r="7" ht="144" customHeight="1" spans="1:6">
       <c r="A7" s="2"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="8" ht="144" customHeight="1" spans="1:6">
+    <row r="8" ht="84" spans="1:6">
       <c r="A8" s="2"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="26" t="s">
-        <v>26</v>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="9" ht="84" spans="1:6">
+    <row r="9" ht="309" customHeight="1" spans="1:6">
       <c r="A9" s="2"/>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26" t="s">
-        <v>26</v>
+      <c r="E9" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="10" ht="309" customHeight="1" spans="1:6">
+    <row r="10" ht="188" customHeight="1" spans="1:6">
       <c r="A10" s="2"/>
-      <c r="B10" s="20" t="s">
-        <v>33</v>
+      <c r="B10" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="D10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>26</v>
+      <c r="E10" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="11" ht="188" customHeight="1" spans="1:6">
+    <row r="11" ht="118" spans="1:6">
       <c r="A11" s="2"/>
-      <c r="B11" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>26</v>
+      <c r="F11" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="12" ht="101" spans="1:6">
+    <row r="12" ht="110" customHeight="1" spans="1:6">
       <c r="A12" s="2"/>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="C12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>26</v>
+      <c r="F12" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="13" ht="101" spans="1:6">
+    <row r="13" ht="51" spans="1:6">
       <c r="A13" s="2"/>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="D13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>26</v>
+      <c r="E13" s="27"/>
+      <c r="F13" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="14" ht="51" spans="1:6">
+    <row r="14" ht="55" customHeight="1" spans="1:6">
       <c r="A14" s="2"/>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="51" spans="1:6">
+      <c r="A15" s="2"/>
+      <c r="B15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" ht="55" customHeight="1" spans="1:6">
-      <c r="A15" s="2"/>
-      <c r="B15" s="20" t="s">
+      <c r="C15" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" ht="51" spans="1:6">
-      <c r="A16" s="2"/>
-      <c r="B16" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="26" t="s">
-        <v>26</v>
+      <c r="E15" s="27"/>
+      <c r="F15" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A2:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
